--- a/タスク表.xlsx
+++ b/タスク表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\中平　悠希\Desktop\GitHub\2025Summer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\y_nakahira\Documents\GitHub\2025Summer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A70EEDBA-C989-4001-9A45-82CA3B64D882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B643B101-0C4A-434E-9BB9-658D7F8ED961}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25200" yWindow="3690" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1498,90 +1498,7 @@
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="24">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE2EEB6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFCCFF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF5EECCA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFEE7460"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF1F17F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC3F088"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7995EF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF8DEFE6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
+  <dxfs count="12">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1947,6 +1864,7 @@
     <col min="2" max="2" width="32.25" customWidth="1"/>
     <col min="3" max="3" width="38.375" customWidth="1"/>
     <col min="4" max="4" width="22.25" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -2070,11 +1988,11 @@
         <v>3</v>
       </c>
       <c r="F12" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
@@ -2174,11 +2092,11 @@
         <v>10</v>
       </c>
       <c r="F16" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
@@ -2200,11 +2118,11 @@
         <v>3</v>
       </c>
       <c r="F17" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H17" s="4"/>
       <c r="I17" s="4"/>
@@ -2330,11 +2248,11 @@
         <v>2</v>
       </c>
       <c r="F22" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H22" s="4"/>
       <c r="I22" s="4"/>
@@ -2382,11 +2300,11 @@
         <v>2</v>
       </c>
       <c r="F24" s="7">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G24" s="8">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
@@ -2434,11 +2352,11 @@
         <v>15</v>
       </c>
       <c r="F26" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H26" s="4"/>
       <c r="I26" s="4"/>
@@ -2486,11 +2404,11 @@
         <v>15</v>
       </c>
       <c r="F28" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
@@ -2538,11 +2456,11 @@
         <v>10</v>
       </c>
       <c r="F30" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H30" s="4"/>
       <c r="I30" s="4"/>
@@ -2564,11 +2482,11 @@
         <v>10</v>
       </c>
       <c r="F31" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H31" s="4"/>
       <c r="I31" s="4"/>
@@ -2590,11 +2508,11 @@
         <v>5</v>
       </c>
       <c r="F32" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
@@ -2752,11 +2670,11 @@
         <v>2</v>
       </c>
       <c r="F38" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H38" s="4"/>
       <c r="I38" s="4"/>
@@ -2804,11 +2722,11 @@
         <v>4</v>
       </c>
       <c r="F40" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G40" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H40" s="4"/>
       <c r="I40" s="4"/>
@@ -2830,11 +2748,11 @@
         <v>3</v>
       </c>
       <c r="F41" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G41" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H41" s="4"/>
       <c r="I41" s="4"/>
@@ -2856,11 +2774,11 @@
         <v>5</v>
       </c>
       <c r="F42" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G42" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H42" s="4"/>
       <c r="I42" s="4"/>
@@ -2934,11 +2852,11 @@
         <v>4</v>
       </c>
       <c r="F45" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G45" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H45" s="4"/>
       <c r="I45" s="4"/>
@@ -2960,11 +2878,11 @@
         <v>4</v>
       </c>
       <c r="F46" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G46" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H46" s="4"/>
       <c r="I46" s="4"/>
@@ -2986,11 +2904,11 @@
         <v>3</v>
       </c>
       <c r="F47" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G47" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H47" s="4"/>
       <c r="I47" s="4"/>
@@ -3012,11 +2930,11 @@
         <v>4</v>
       </c>
       <c r="F48" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G48" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H48" s="4"/>
       <c r="I48" s="4"/>
@@ -3064,11 +2982,11 @@
         <v>2</v>
       </c>
       <c r="F50" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G50" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H50" s="4"/>
       <c r="I50" s="4"/>
@@ -3090,11 +3008,11 @@
         <v>2</v>
       </c>
       <c r="F51" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G51" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H51" s="4"/>
       <c r="I51" s="4"/>
@@ -3116,11 +3034,11 @@
         <v>2</v>
       </c>
       <c r="F52" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G52" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H52" s="4"/>
       <c r="I52" s="4"/>
@@ -3142,11 +3060,11 @@
         <v>2</v>
       </c>
       <c r="F53" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G53" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H53" s="4"/>
       <c r="I53" s="4"/>
@@ -3168,11 +3086,11 @@
         <v>2</v>
       </c>
       <c r="F54" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G54" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H54" s="4"/>
       <c r="I54" s="4"/>
@@ -3220,11 +3138,11 @@
         <v>2</v>
       </c>
       <c r="F56" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G56" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H56" s="4"/>
       <c r="I56" s="4"/>
@@ -3246,11 +3164,11 @@
         <v>1</v>
       </c>
       <c r="F57" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G57" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H57" s="4"/>
       <c r="I57" s="4"/>
@@ -3272,11 +3190,11 @@
         <v>5</v>
       </c>
       <c r="F58" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G58" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H58" s="4"/>
       <c r="I58" s="4"/>
@@ -3298,11 +3216,11 @@
         <v>3</v>
       </c>
       <c r="F59" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G59" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H59" s="4"/>
       <c r="I59" s="4"/>
@@ -3324,11 +3242,11 @@
         <v>3</v>
       </c>
       <c r="F60" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G60" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H60" s="4"/>
       <c r="I60" s="4"/>
@@ -3454,11 +3372,11 @@
         <v>1</v>
       </c>
       <c r="F65" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G65" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H65" s="4"/>
       <c r="I65" s="4"/>
@@ -3480,11 +3398,11 @@
         <v>5</v>
       </c>
       <c r="F66" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G66" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H66" s="4"/>
       <c r="I66" s="4"/>
@@ -3532,11 +3450,11 @@
         <v>3</v>
       </c>
       <c r="F68" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G68" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H68" s="4"/>
       <c r="I68" s="4"/>
@@ -3558,11 +3476,11 @@
         <v>3</v>
       </c>
       <c r="F69" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G69" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H69" s="4"/>
       <c r="I69" s="4"/>
@@ -3714,11 +3632,11 @@
         <v>2</v>
       </c>
       <c r="F75" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G75" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H75" s="4"/>
       <c r="I75" s="4"/>
@@ -3740,11 +3658,11 @@
         <v>5</v>
       </c>
       <c r="F76" s="7">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G76" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="H76" s="4"/>
       <c r="I76" s="4"/>
@@ -4156,11 +4074,11 @@
         <v>5</v>
       </c>
       <c r="F92" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G92" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H92" s="4"/>
       <c r="I92" s="4"/>
@@ -4182,11 +4100,11 @@
         <v>7</v>
       </c>
       <c r="F93" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G93" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H93" s="4"/>
       <c r="I93" s="4"/>
@@ -4314,11 +4232,11 @@
         <v>3</v>
       </c>
       <c r="F98" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G98" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H98" s="4"/>
       <c r="I98" s="4"/>
@@ -4366,11 +4284,11 @@
         <v>2</v>
       </c>
       <c r="F100" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G100" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H100" s="4"/>
       <c r="I100" s="4"/>
@@ -4444,11 +4362,11 @@
         <v>5</v>
       </c>
       <c r="F103" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G103" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H103" s="4"/>
       <c r="I103" s="4"/>
@@ -4574,11 +4492,11 @@
         <v>1</v>
       </c>
       <c r="F108" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G108" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H108" s="4"/>
       <c r="I108" s="4"/>
@@ -4600,11 +4518,11 @@
         <v>1</v>
       </c>
       <c r="F109" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G109" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H109" s="4"/>
       <c r="I109" s="4"/>
@@ -4704,11 +4622,11 @@
         <v>3</v>
       </c>
       <c r="F113" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G113" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H113" s="4"/>
       <c r="I113" s="4"/>
@@ -4730,11 +4648,11 @@
         <v>3</v>
       </c>
       <c r="F114" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G114" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H114" s="4"/>
       <c r="I114" s="4"/>
@@ -4872,7 +4790,7 @@
       <c r="K119" s="4"/>
       <c r="L119" s="4"/>
     </row>
-    <row r="120" spans="2:12" ht="113.25" thickBot="1">
+    <row r="120" spans="2:12" ht="38.25" thickBot="1">
       <c r="B120" s="10" t="s">
         <v>133</v>
       </c>
@@ -4911,7 +4829,7 @@
       <c r="F121" s="2"/>
       <c r="G121" s="3">
         <f>SUM(G10:G120)</f>
-        <v>21.25</v>
+        <v>194.75</v>
       </c>
       <c r="H121" s="4"/>
       <c r="I121" s="4"/>
@@ -4972,7 +4890,7 @@
       <c r="E125" s="4"/>
       <c r="F125" s="4">
         <f>SUM(G10:G120)</f>
-        <v>21.25</v>
+        <v>194.75</v>
       </c>
       <c r="G125" s="4"/>
       <c r="H125" s="4"/>
@@ -4990,7 +4908,7 @@
       <c r="E126" s="4"/>
       <c r="F126" s="15">
         <f>F125/F124</f>
-        <v>3.7477954144620809E-2</v>
+        <v>0.34347442680776014</v>
       </c>
       <c r="G126" s="4"/>
       <c r="H126" s="4"/>
@@ -5057,7 +4975,7 @@
       <c r="E130" s="4"/>
       <c r="F130" s="16">
         <f ca="1">TODAY()</f>
-        <v>45819</v>
+        <v>45891</v>
       </c>
       <c r="G130" s="4"/>
       <c r="H130" s="4"/>
@@ -5075,7 +4993,7 @@
       <c r="E131" s="4"/>
       <c r="F131" s="4">
         <f ca="1">F129-F130</f>
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="G131" s="4" t="s">
         <v>144</v>
@@ -5084,9 +5002,9 @@
         <v>145</v>
       </c>
       <c r="I131" s="4"/>
-      <c r="J131" s="17">
+      <c r="J131" s="17" t="e">
         <f ca="1">(F124-F125)/F131</f>
-        <v>7.5798611111111107</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="K131" s="4" t="s">
         <v>146</v>
@@ -5102,7 +5020,7 @@
       <c r="E132" s="4"/>
       <c r="F132" s="15">
         <f ca="1">1-(F131/(F129-F128))</f>
-        <v>0.49650349650349646</v>
+        <v>1</v>
       </c>
       <c r="G132" s="4"/>
       <c r="H132" s="4"/>
